--- a/output/pdf_financials_xlsx/YOO.xlsx
+++ b/output/pdf_financials_xlsx/YOO.xlsx
@@ -6717,19 +6717,19 @@
         <v>0</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>1.002193</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>1.157622</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>1.157622</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>1.157622</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>1.157622</v>
       </c>
     </row>
     <row r="92">
@@ -6775,22 +6775,22 @@
         <v>6.851029</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.035352</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.982586</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.971266</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.971266</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>5.971266</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>6.005729</v>
       </c>
     </row>
     <row r="93">
@@ -12184,7 +12184,11 @@
           <t>Share-Based Payments Reserve (note 16)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -12288,7 +12292,11 @@
           <t>Foreign Currency Translation Reserve</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -17328,7 +17336,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -17422,7 +17434,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -23612,7 +23628,11 @@
           <t>Share-based payments reserve 5,971,266</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -23712,7 +23732,11 @@
           <t>Foreign currency translation reserve 1,157,622</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/YOO.xlsx
+++ b/output/pdf_financials_xlsx/YOO.xlsx
@@ -1254,19 +1254,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.011074</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004327</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.004201</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001766</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.002596</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -2553,19 +2553,19 @@
         <v>-6.667316</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.644576</v>
+        <v>-5.65565</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-8.467002000000001</v>
+        <v>-8.471329000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.613295</v>
+        <v>-4.617496</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.235052</v>
+        <v>-2.236818</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.630434</v>
+        <v>-1.63303</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -2723,19 +2723,19 @@
         <v>-6.667316</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.644576</v>
+        <v>-5.65565</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.800072</v>
+        <v>-7.804399</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.531082</v>
+        <v>-4.535283</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.235052</v>
+        <v>-2.236818</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.630434</v>
+        <v>-1.63303</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2808,19 +2808,19 @@
         <v>-1151.894653368186</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-723.6162763716731</v>
+        <v>-725.0359271380975</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-967.1604926025304</v>
+        <v>-967.6970137335521</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-312.5119060674216</v>
+        <v>-312.8016519862528</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-83.08082554027301</v>
+        <v>-83.14647087555116</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-46.65728046152658</v>
+        <v>-46.73156884123291</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         <v>0.396705</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.354579</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.215554</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>1.441716</v>
@@ -3103,22 +3103,22 @@
         <v>1.570483</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.861253</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.46187</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.296748</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.150928</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.231083</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.161112</v>
       </c>
     </row>
     <row r="35">
@@ -3213,10 +3213,10 @@
         <v>0.396705</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.354579</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.215554</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>1.441716</v>
@@ -3225,22 +3225,22 @@
         <v>1.570483</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.861253</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.46187</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.296748</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.150928</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.231083</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.161112</v>
       </c>
     </row>
     <row r="37">
@@ -3945,10 +3945,10 @@
         <v>0.203658</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.573381</v>
+        <v>0.218802</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.526828</v>
+        <v>0.311274</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.438123</v>
@@ -3957,22 +3957,22 @@
         <v>0.472921</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.382886</v>
+        <v>0.521633</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.871573</v>
+        <v>0.409703</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.8452</v>
+        <v>0.5484520000000001</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.417022</v>
+        <v>0.266094</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.416663</v>
+        <v>0.18558</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.317588</v>
+        <v>0.156476</v>
       </c>
     </row>
     <row r="49">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -21606,7 +21606,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -25280,7 +25280,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -63306,7 +63306,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -63410,7 +63410,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -65188,7 +65188,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -65296,7 +65296,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">

--- a/output/pdf_financials_xlsx/YOO.xlsx
+++ b/output/pdf_financials_xlsx/YOO.xlsx
@@ -2641,16 +2641,16 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.66693</v>
+        <v>0.08780399999999999</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0.08221299999999999</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.069465</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.075902</v>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
@@ -2726,16 +2726,16 @@
         <v>-5.65565</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.804399</v>
+        <v>-8.383525000000001</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-4.535283</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.236818</v>
+        <v>-2.167353</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.63303</v>
+        <v>-1.557128</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2811,16 +2811,16 @@
         <v>-725.0359271380975</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-967.6970137335521</v>
+        <v>-1039.505041587517</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-312.8016519862528</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-83.14647087555116</v>
+        <v>-80.5643342871608</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-46.73156884123291</v>
+        <v>-44.55952084567419</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -7209,10 +7209,10 @@
         <v>0.08221299999999999</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.069465</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.075902</v>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
@@ -7225,16 +7225,16 @@
         </is>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.125651</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.115437</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.11341</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.25772</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
@@ -8507,16 +8507,16 @@
         <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>1.948069</v>
       </c>
       <c r="E120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>1.284706</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>1.29479</v>
       </c>
       <c r="H120" s="1" t="inlineStr">
         <is>
@@ -51594,7 +51594,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -54410,7 +54414,11 @@
           <t>Depreciation of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -56722,7 +56730,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -58728,7 +58740,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -61234,7 +61250,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
           <t>-</t>
@@ -62996,7 +63016,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -64240,7 +64264,11 @@
           <t>Depreciation of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E525" t="inlineStr">
         <is>
           <t>-</t>
